--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E804"/>
+  <dimension ref="A1:E806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17316,6 +17316,48 @@
         <v>164.6</v>
       </c>
       <c r="E804" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>169.94</v>
+      </c>
+      <c r="C805" t="n">
+        <v>437.65</v>
+      </c>
+      <c r="D805" t="n">
+        <v>161.76</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>173.11</v>
+      </c>
+      <c r="C806" t="n">
+        <v>437.25</v>
+      </c>
+      <c r="D806" t="n">
+        <v>162.05</v>
+      </c>
+      <c r="E806" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17332,7 +17374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B864"/>
+  <dimension ref="A1:B866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25975,6 +26017,26 @@
       </c>
       <c r="B864" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -26137,28 +26199,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2408629520638744</v>
+        <v>-0.2428271276118419</v>
       </c>
       <c r="J2" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="K2" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04320816723444643</v>
+        <v>0.04408236614613414</v>
       </c>
       <c r="M2" t="n">
-        <v>7.458378337126161</v>
+        <v>7.449966646412588</v>
       </c>
       <c r="N2" t="n">
-        <v>72.14851891026527</v>
+        <v>72.01608522039062</v>
       </c>
       <c r="O2" t="n">
-        <v>8.494028426504427</v>
+        <v>8.486229152008011</v>
       </c>
       <c r="P2" t="n">
-        <v>181.9120081527109</v>
+        <v>181.931979595403</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26209,28 +26271,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08276009676136405</v>
+        <v>-0.0816130766685363</v>
       </c>
       <c r="J3" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="K3" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04460612265160435</v>
+        <v>0.04358386197645314</v>
       </c>
       <c r="M3" t="n">
-        <v>2.164237716557008</v>
+        <v>2.164852053753968</v>
       </c>
       <c r="N3" t="n">
-        <v>8.238834050885931</v>
+        <v>8.232281530456074</v>
       </c>
       <c r="O3" t="n">
-        <v>2.870336922886568</v>
+        <v>2.869195275762191</v>
       </c>
       <c r="P3" t="n">
-        <v>437.2581998010118</v>
+        <v>437.2465332604106</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26281,28 +26343,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2497268247948265</v>
+        <v>-0.251602510921814</v>
       </c>
       <c r="J4" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="K4" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1004672551489598</v>
+        <v>0.1022098401919056</v>
       </c>
       <c r="M4" t="n">
-        <v>4.809267370764906</v>
+        <v>4.808496472462885</v>
       </c>
       <c r="N4" t="n">
-        <v>31.35874162053886</v>
+        <v>31.31782566402128</v>
       </c>
       <c r="O4" t="n">
-        <v>5.59988764356383</v>
+        <v>5.596233167410136</v>
       </c>
       <c r="P4" t="n">
-        <v>172.3377338211654</v>
+        <v>172.3568126852634</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26340,7 +26402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E804"/>
+  <dimension ref="A1:E806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48051,6 +48113,60 @@
         </is>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>-39.33601274636195,176.93765638374032</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>-39.33659656469514,176.93576741574995</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>-39.336041035254006,176.93766108876156</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>-39.336598198506266,176.93577003586844</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E806"/>
+  <dimension ref="A1:E808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17360,6 +17360,48 @@
       <c r="E806" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="C807" t="n">
+        <v>439.34</v>
+      </c>
+      <c r="D807" t="n">
+        <v>164.62</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:54:21+00:00</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>176.25</v>
+      </c>
+      <c r="C808" t="n">
+        <v>440.19</v>
+      </c>
+      <c r="D808" t="n">
+        <v>165.35</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -17374,7 +17416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B866"/>
+  <dimension ref="A1:B868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26037,6 +26079,26 @@
       </c>
       <c r="B866" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -26199,28 +26261,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2428271276118419</v>
+        <v>-0.2428207661018508</v>
       </c>
       <c r="J2" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="K2" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04408236614613414</v>
+        <v>0.04430494580020716</v>
       </c>
       <c r="M2" t="n">
-        <v>7.449966646412588</v>
+        <v>7.433243223711565</v>
       </c>
       <c r="N2" t="n">
-        <v>72.01608522039062</v>
+        <v>71.83882885026414</v>
       </c>
       <c r="O2" t="n">
-        <v>8.486229152008011</v>
+        <v>8.475778952418718</v>
       </c>
       <c r="P2" t="n">
-        <v>181.931979595403</v>
+        <v>181.9319145394457</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26271,28 +26333,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0816130766685363</v>
+        <v>-0.07935834631499367</v>
       </c>
       <c r="J3" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="K3" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04358386197645314</v>
+        <v>0.0412585069724577</v>
       </c>
       <c r="M3" t="n">
-        <v>2.164852053753968</v>
+        <v>2.17118358857325</v>
       </c>
       <c r="N3" t="n">
-        <v>8.232281530456074</v>
+        <v>8.265967603720757</v>
       </c>
       <c r="O3" t="n">
-        <v>2.869195275762191</v>
+        <v>2.875059582638377</v>
       </c>
       <c r="P3" t="n">
-        <v>437.2465332604106</v>
+        <v>437.2235518739184</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26343,28 +26405,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.251602510921814</v>
+        <v>-0.2519622346883462</v>
       </c>
       <c r="J4" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="K4" t="n">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1022098401919056</v>
+        <v>0.1029593944897812</v>
       </c>
       <c r="M4" t="n">
-        <v>4.808496472462885</v>
+        <v>4.798716879170192</v>
       </c>
       <c r="N4" t="n">
-        <v>31.31782566402128</v>
+        <v>31.24190376660933</v>
       </c>
       <c r="O4" t="n">
-        <v>5.596233167410136</v>
+        <v>5.589445747711425</v>
       </c>
       <c r="P4" t="n">
-        <v>172.3568126852634</v>
+        <v>172.3604790442476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26402,7 +26464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E806"/>
+  <dimension ref="A1:E808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48167,6 +48229,60 @@
         </is>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>-39.33605656291061,176.93766367133043</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>-39.33661267745025,176.9357932555443</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:54:21+00:00</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>-39.336069056427334,176.93766574926045</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>-39.33661679014546,176.93579985101817</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E808"/>
+  <dimension ref="A1:E809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17402,6 +17402,27 @@
       <c r="E808" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>179.47</v>
+      </c>
+      <c r="C809" t="n">
+        <v>439.76</v>
+      </c>
+      <c r="D809" t="n">
+        <v>168.34</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B868"/>
+  <dimension ref="A1:B869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26099,6 +26120,16 @@
       </c>
       <c r="B868" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -26261,28 +26292,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2428207661018508</v>
+        <v>-0.241862369988516</v>
       </c>
       <c r="J2" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K2" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04430494580020716</v>
+        <v>0.04407316476585121</v>
       </c>
       <c r="M2" t="n">
-        <v>7.433243223711565</v>
+        <v>7.428899946099397</v>
       </c>
       <c r="N2" t="n">
-        <v>71.83882885026414</v>
+        <v>71.76920459135452</v>
       </c>
       <c r="O2" t="n">
-        <v>8.475778952418718</v>
+        <v>8.471670708387721</v>
       </c>
       <c r="P2" t="n">
-        <v>181.9319145394457</v>
+        <v>181.9221078553067</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26333,28 +26364,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07935834631499367</v>
+        <v>-0.07823672542068394</v>
       </c>
       <c r="J3" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K3" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0412585069724577</v>
+        <v>0.04012756588821775</v>
       </c>
       <c r="M3" t="n">
-        <v>2.17118358857325</v>
+        <v>2.174268531073124</v>
       </c>
       <c r="N3" t="n">
-        <v>8.265967603720757</v>
+        <v>8.282150939730931</v>
       </c>
       <c r="O3" t="n">
-        <v>2.875059582638377</v>
+        <v>2.877872641332644</v>
       </c>
       <c r="P3" t="n">
-        <v>437.2235518739184</v>
+        <v>437.2120750099357</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26405,28 +26436,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2519622346883462</v>
+        <v>-0.2513233587543649</v>
       </c>
       <c r="J4" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="K4" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1029593944897812</v>
+        <v>0.1027138184299169</v>
       </c>
       <c r="M4" t="n">
-        <v>4.798716879170192</v>
+        <v>4.795515616577453</v>
       </c>
       <c r="N4" t="n">
-        <v>31.24190376660933</v>
+        <v>31.21180776602218</v>
       </c>
       <c r="O4" t="n">
-        <v>5.589445747711425</v>
+        <v>5.586752882133071</v>
       </c>
       <c r="P4" t="n">
-        <v>172.3604790442476</v>
+        <v>172.353941815641</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26464,7 +26495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E808"/>
+  <dimension ref="A1:E809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48283,6 +48314,33 @@
         </is>
       </c>
     </row>
+    <row r="809">
+      <c r="A809" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>-39.33609779151543,176.93767052850302</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>-39.33663363529,176.9358268653643</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E809"/>
+  <dimension ref="A1:E811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17421,6 +17421,48 @@
         <v>168.34</v>
       </c>
       <c r="E809" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="C810" t="n">
+        <v>439.86</v>
+      </c>
+      <c r="D810" t="n">
+        <v>169.64</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>186.78</v>
+      </c>
+      <c r="C811" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="D811" t="n">
+        <v>171.54</v>
+      </c>
+      <c r="E811" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17437,7 +17479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B869"/>
+  <dimension ref="A1:B871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26130,6 +26172,26 @@
       </c>
       <c r="B869" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -26292,28 +26354,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.241862369988516</v>
+        <v>-0.237459713423344</v>
       </c>
       <c r="J2" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="K2" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04407316476585121</v>
+        <v>0.0426506245198357</v>
       </c>
       <c r="M2" t="n">
-        <v>7.428899946099397</v>
+        <v>7.432627340393207</v>
       </c>
       <c r="N2" t="n">
-        <v>71.76920459135452</v>
+        <v>71.80575308564364</v>
       </c>
       <c r="O2" t="n">
-        <v>8.471670708387721</v>
+        <v>8.473827534570411</v>
       </c>
       <c r="P2" t="n">
-        <v>181.9221078553067</v>
+        <v>181.8768655430248</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26364,28 +26426,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07823672542068394</v>
+        <v>-0.07510070775464731</v>
       </c>
       <c r="J3" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="K3" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04012756588821775</v>
+        <v>0.03681466913908371</v>
       </c>
       <c r="M3" t="n">
-        <v>2.174268531073124</v>
+        <v>2.185180837391146</v>
       </c>
       <c r="N3" t="n">
-        <v>8.282150939730931</v>
+        <v>8.37165489015762</v>
       </c>
       <c r="O3" t="n">
-        <v>2.877872641332644</v>
+        <v>2.893381221021112</v>
       </c>
       <c r="P3" t="n">
-        <v>437.2120750099357</v>
+        <v>437.179847957017</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26436,28 +26498,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2513233587543649</v>
+        <v>-0.2489491903366447</v>
       </c>
       <c r="J4" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="K4" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1027138184299169</v>
+        <v>0.1012929147876085</v>
       </c>
       <c r="M4" t="n">
-        <v>4.795515616577453</v>
+        <v>4.793790295602416</v>
       </c>
       <c r="N4" t="n">
-        <v>31.21180776602218</v>
+        <v>31.19570699172615</v>
       </c>
       <c r="O4" t="n">
-        <v>5.586752882133071</v>
+        <v>5.585311718402667</v>
       </c>
       <c r="P4" t="n">
-        <v>172.353941815641</v>
+        <v>172.3295456406085</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26495,7 +26557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E809"/>
+  <dimension ref="A1:E811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48341,6 +48403,60 @@
         </is>
       </c>
     </row>
+    <row r="810">
+      <c r="A810" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>-39.336123938660364,176.93767487732114</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>-39.33664095926371,176.93583861073617</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>-39.33616302551788,176.93768137829233</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>-39.33665166353061,176.93585577705326</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E811"/>
+  <dimension ref="A1:E814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17463,6 +17463,69 @@
         <v>171.54</v>
       </c>
       <c r="E811" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>188.43</v>
+      </c>
+      <c r="C812" t="n">
+        <v>441.25</v>
+      </c>
+      <c r="D812" t="n">
+        <v>171.44</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:33+00:00</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>188.59</v>
+      </c>
+      <c r="C813" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="D813" t="n">
+        <v>171.11</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:13+00:00</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>188.88</v>
+      </c>
+      <c r="C814" t="n">
+        <v>439.69</v>
+      </c>
+      <c r="D814" t="n">
+        <v>171.46</v>
+      </c>
+      <c r="E814" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17479,7 +17542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B871"/>
+  <dimension ref="A1:B874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26192,6 +26255,36 @@
       </c>
       <c r="B871" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -26354,28 +26447,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.237459713423344</v>
+        <v>-0.2280165918198596</v>
       </c>
       <c r="J2" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K2" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0426506245198357</v>
+        <v>0.0394367352231374</v>
       </c>
       <c r="M2" t="n">
-        <v>7.432627340393207</v>
+        <v>7.452943125445056</v>
       </c>
       <c r="N2" t="n">
-        <v>71.80575308564364</v>
+        <v>72.16343556707329</v>
       </c>
       <c r="O2" t="n">
-        <v>8.473827534570411</v>
+        <v>8.494906448400318</v>
       </c>
       <c r="P2" t="n">
-        <v>181.8768655430248</v>
+        <v>181.7795703021666</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26426,28 +26519,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07510070775464731</v>
+        <v>-0.07096989035481664</v>
       </c>
       <c r="J3" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K3" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03681466913908371</v>
+        <v>0.03280276625600897</v>
       </c>
       <c r="M3" t="n">
-        <v>2.185180837391146</v>
+        <v>2.198733880276688</v>
       </c>
       <c r="N3" t="n">
-        <v>8.37165489015762</v>
+        <v>8.462761993213356</v>
       </c>
       <c r="O3" t="n">
-        <v>2.893381221021112</v>
+        <v>2.909082672117339</v>
       </c>
       <c r="P3" t="n">
-        <v>437.179847957017</v>
+        <v>437.1372907705003</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26498,28 +26591,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2489491903366447</v>
+        <v>-0.244884608152612</v>
       </c>
       <c r="J4" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="K4" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1012929147876085</v>
+        <v>0.09872769708927776</v>
       </c>
       <c r="M4" t="n">
-        <v>4.793790295602416</v>
+        <v>4.793389337590646</v>
       </c>
       <c r="N4" t="n">
-        <v>31.19570699172615</v>
+        <v>31.19602632830739</v>
       </c>
       <c r="O4" t="n">
-        <v>5.585311718402667</v>
+        <v>5.585340305505779</v>
       </c>
       <c r="P4" t="n">
-        <v>172.3295456406085</v>
+        <v>172.287667454849</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26557,7 +26650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E811"/>
+  <dimension ref="A1:E814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48457,6 +48550,87 @@
         </is>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>-39.336177750018756,176.93768382729067</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>-39.3366511001482,176.93585487356276</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:33+00:00</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>-39.33617917784914,176.93768406476937</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>-39.33664924098624,176.9358518920442</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:13+00:00</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>-39.33618176579169,176.93768449519953</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>-39.33665121282469,176.93585505426086</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E814"/>
+  <dimension ref="A1:E815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17526,6 +17526,27 @@
         <v>171.46</v>
       </c>
       <c r="E814" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-24 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>188.88</v>
+      </c>
+      <c r="C815" t="n">
+        <v>439.28</v>
+      </c>
+      <c r="D815" t="n">
+        <v>171.46</v>
+      </c>
+      <c r="E815" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17542,7 +17563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B874"/>
+  <dimension ref="A1:B875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26285,6 +26306,16 @@
       </c>
       <c r="B874" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-03-24 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -26447,28 +26478,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2280165918198596</v>
+        <v>-0.2248450343175458</v>
       </c>
       <c r="J2" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0394367352231374</v>
+        <v>0.03838045954369862</v>
       </c>
       <c r="M2" t="n">
-        <v>7.452943125445056</v>
+        <v>7.459834411881259</v>
       </c>
       <c r="N2" t="n">
-        <v>72.16343556707329</v>
+        <v>72.28683555240234</v>
       </c>
       <c r="O2" t="n">
-        <v>8.494906448400318</v>
+        <v>8.502166521093452</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7795703021666</v>
+        <v>181.7468285383115</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26519,28 +26550,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07096989035481664</v>
+        <v>-0.0699995107647398</v>
       </c>
       <c r="J3" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K3" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03280276625600897</v>
+        <v>0.03195138128353858</v>
       </c>
       <c r="M3" t="n">
-        <v>2.198733880276688</v>
+        <v>2.201167708439788</v>
       </c>
       <c r="N3" t="n">
-        <v>8.462761993213356</v>
+        <v>8.472216473357118</v>
       </c>
       <c r="O3" t="n">
-        <v>2.909082672117339</v>
+        <v>2.910707211891488</v>
       </c>
       <c r="P3" t="n">
-        <v>437.1372907705003</v>
+        <v>437.1272729986752</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26591,28 +26622,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.244884608152612</v>
+        <v>-0.2435127693097962</v>
       </c>
       <c r="J4" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K4" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09872769708927776</v>
+        <v>0.09785870802151109</v>
       </c>
       <c r="M4" t="n">
-        <v>4.793389337590646</v>
+        <v>4.793388074499287</v>
       </c>
       <c r="N4" t="n">
-        <v>31.19602632830739</v>
+        <v>31.19737589357511</v>
       </c>
       <c r="O4" t="n">
-        <v>5.585340305505779</v>
+        <v>5.585461117363105</v>
       </c>
       <c r="P4" t="n">
-        <v>172.287667454849</v>
+        <v>172.2735051943804</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26650,7 +26681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E814"/>
+  <dimension ref="A1:E815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48631,6 +48662,33 @@
         </is>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-24 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>-39.33618176579169,176.93768449519953</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>-39.33665121282469,176.93585505426086</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E815"/>
+  <dimension ref="A1:E819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17547,6 +17547,90 @@
         <v>171.46</v>
       </c>
       <c r="E815" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>187.83</v>
+      </c>
+      <c r="C816" t="n">
+        <v>438.47</v>
+      </c>
+      <c r="D816" t="n">
+        <v>171.29</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="C817" t="n">
+        <v>438.79</v>
+      </c>
+      <c r="D817" t="n">
+        <v>170.85</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="C818" t="n">
+        <v>437.83</v>
+      </c>
+      <c r="D818" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="C819" t="n">
+        <v>437.56</v>
+      </c>
+      <c r="D819" t="n">
+        <v>170.45</v>
+      </c>
+      <c r="E819" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17563,7 +17647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B875"/>
+  <dimension ref="A1:B879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26316,6 +26400,46 @@
       </c>
       <c r="B875" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
@@ -26478,28 +26602,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2248450343175458</v>
+        <v>-0.2151753226817765</v>
       </c>
       <c r="J2" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="K2" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03838045954369862</v>
+        <v>0.03539272138161387</v>
       </c>
       <c r="M2" t="n">
-        <v>7.459834411881259</v>
+        <v>7.472016323926515</v>
       </c>
       <c r="N2" t="n">
-        <v>72.28683555240234</v>
+        <v>72.43904288190161</v>
       </c>
       <c r="O2" t="n">
-        <v>8.502166521093452</v>
+        <v>8.511112905014338</v>
       </c>
       <c r="P2" t="n">
-        <v>181.7468285383115</v>
+        <v>181.6467839139781</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26550,28 +26674,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0699995107647398</v>
+        <v>-0.06723426021479803</v>
       </c>
       <c r="J3" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="K3" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03195138128353858</v>
+        <v>0.02971795729345006</v>
       </c>
       <c r="M3" t="n">
-        <v>2.201167708439788</v>
+        <v>2.205216956217847</v>
       </c>
       <c r="N3" t="n">
-        <v>8.472216473357118</v>
+        <v>8.472498509902556</v>
       </c>
       <c r="O3" t="n">
-        <v>2.910707211891488</v>
+        <v>2.910755659601568</v>
       </c>
       <c r="P3" t="n">
-        <v>437.1272729986752</v>
+        <v>437.0986633373444</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26622,28 +26746,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2435127693097962</v>
+        <v>-0.2387704790959685</v>
       </c>
       <c r="J4" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="K4" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09785870802151109</v>
+        <v>0.09503487902708818</v>
       </c>
       <c r="M4" t="n">
-        <v>4.793388074499287</v>
+        <v>4.790240184027232</v>
       </c>
       <c r="N4" t="n">
-        <v>31.19737589357511</v>
+        <v>31.1645798823048</v>
       </c>
       <c r="O4" t="n">
-        <v>5.585461117363105</v>
+        <v>5.582524507989625</v>
       </c>
       <c r="P4" t="n">
-        <v>172.2735051943804</v>
+        <v>172.2244364538777</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26681,7 +26805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E815"/>
+  <dimension ref="A1:E819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48689,6 +48813,114 @@
         </is>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>-39.33617239565481,176.93768293674566</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>-39.336650255074595,176.93585351832704</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>-39.33616097301169,176.9376810369169</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>-39.3366477761919,176.9358495429691</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>-39.336149014932076,176.9376790480345</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>-39.33664540998555,176.93584574830948</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>-39.33613812772518,176.9376772372617</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>-39.336645522662046,176.93584592900754</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E819"/>
+  <dimension ref="A1:E823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17631,6 +17631,90 @@
         <v>170.45</v>
       </c>
       <c r="E819" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="C820" t="n">
+        <v>437.04</v>
+      </c>
+      <c r="D820" t="n">
+        <v>169.95</v>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>181.27</v>
+      </c>
+      <c r="C821" t="n">
+        <v>437.12</v>
+      </c>
+      <c r="D821" t="n">
+        <v>169.81</v>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>179.96</v>
+      </c>
+      <c r="C822" t="n">
+        <v>436.74</v>
+      </c>
+      <c r="D822" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>178.09</v>
+      </c>
+      <c r="C823" t="n">
+        <v>436.41</v>
+      </c>
+      <c r="D823" t="n">
+        <v>170.77</v>
+      </c>
+      <c r="E823" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17647,7 +17731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B879"/>
+  <dimension ref="A1:B883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26440,6 +26524,46 @@
       </c>
       <c r="B879" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -26602,28 +26726,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2151753226817765</v>
+        <v>-0.2109153944317403</v>
       </c>
       <c r="J2" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K2" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03539272138161387</v>
+        <v>0.03435597894345033</v>
       </c>
       <c r="M2" t="n">
-        <v>7.472016323926515</v>
+        <v>7.456963124712292</v>
       </c>
       <c r="N2" t="n">
-        <v>72.43904288190161</v>
+        <v>72.19599538090361</v>
       </c>
       <c r="O2" t="n">
-        <v>8.511112905014338</v>
+        <v>8.496822663849329</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6467839139781</v>
+        <v>181.6025712092664</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26674,28 +26798,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06723426021479803</v>
+        <v>-0.0657917411805211</v>
       </c>
       <c r="J3" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K3" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02971795729345006</v>
+        <v>0.02875196124955215</v>
       </c>
       <c r="M3" t="n">
-        <v>2.205216956217847</v>
+        <v>2.202290834584279</v>
       </c>
       <c r="N3" t="n">
-        <v>8.472498509902556</v>
+        <v>8.442814791318089</v>
       </c>
       <c r="O3" t="n">
-        <v>2.910755659601568</v>
+        <v>2.905652214446541</v>
       </c>
       <c r="P3" t="n">
-        <v>437.0986633373444</v>
+        <v>437.0836888975481</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26746,28 +26870,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2387704790959685</v>
+        <v>-0.2345702233891314</v>
       </c>
       <c r="J4" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K4" t="n">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09503487902708818</v>
+        <v>0.09266541978678533</v>
       </c>
       <c r="M4" t="n">
-        <v>4.790240184027232</v>
+        <v>4.78498081485125</v>
       </c>
       <c r="N4" t="n">
-        <v>31.1645798823048</v>
+        <v>31.10837674700241</v>
       </c>
       <c r="O4" t="n">
-        <v>5.582524507989625</v>
+        <v>5.577488390575314</v>
       </c>
       <c r="P4" t="n">
-        <v>172.2244364538777</v>
+        <v>172.1808208856166</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26805,7 +26929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E819"/>
+  <dimension ref="A1:E823"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48921,6 +49045,114 @@
         </is>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>-39.336123046266344,176.93767472889726</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>-39.336642705749554,176.93584141155597</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>-39.33611385460792,176.9376732001314</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>-39.336641917014035,176.9358401466696</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>-39.33610216424618,176.9376712557795</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>-39.33664636773575,176.9358472842431</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>-39.336085476477734,176.93766848025558</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>-39.33664732548594,176.93584882017677</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0563/nzd0563.xlsx
+++ b/data/nzd0563/nzd0563.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E823"/>
+  <dimension ref="A1:E826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17715,6 +17715,69 @@
         <v>170.77</v>
       </c>
       <c r="E823" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>174.52</v>
+      </c>
+      <c r="C824" t="n">
+        <v>434.58</v>
+      </c>
+      <c r="D824" t="n">
+        <v>168.44</v>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>173.44</v>
+      </c>
+      <c r="C825" t="n">
+        <v>434.58</v>
+      </c>
+      <c r="D825" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>173.15</v>
+      </c>
+      <c r="C826" t="n">
+        <v>435.42</v>
+      </c>
+      <c r="D826" t="n">
+        <v>164.43</v>
+      </c>
+      <c r="E826" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17731,7 +17794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B883"/>
+  <dimension ref="A1:B886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26564,6 +26627,36 @@
       </c>
       <c r="B883" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -26726,28 +26819,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2109153944317403</v>
+        <v>-0.2124953389381455</v>
       </c>
       <c r="J2" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K2" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03435597894345033</v>
+        <v>0.03511631556143102</v>
       </c>
       <c r="M2" t="n">
-        <v>7.456963124712292</v>
+        <v>7.438109120592554</v>
       </c>
       <c r="N2" t="n">
-        <v>72.19599538090361</v>
+        <v>71.95269943848143</v>
       </c>
       <c r="O2" t="n">
-        <v>8.496822663849329</v>
+        <v>8.482493704004821</v>
       </c>
       <c r="P2" t="n">
-        <v>181.6025712092664</v>
+        <v>181.6190445965025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26798,28 +26891,28 @@
         <v>0.1099</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0657917411805211</v>
+        <v>-0.06611205705368886</v>
       </c>
       <c r="J3" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K3" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02875196124955215</v>
+        <v>0.02924688234867878</v>
       </c>
       <c r="M3" t="n">
-        <v>2.202290834584279</v>
+        <v>2.19608400943854</v>
       </c>
       <c r="N3" t="n">
-        <v>8.442814791318089</v>
+        <v>8.413424698016826</v>
       </c>
       <c r="O3" t="n">
-        <v>2.905652214446541</v>
+        <v>2.900590405075633</v>
       </c>
       <c r="P3" t="n">
-        <v>437.0836888975481</v>
+        <v>437.0870271724618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26870,28 +26963,28 @@
         <v>0.0743</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2345702233891314</v>
+        <v>-0.2344016271994871</v>
       </c>
       <c r="J4" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K4" t="n">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09266541978678533</v>
+        <v>0.09319123763279613</v>
       </c>
       <c r="M4" t="n">
-        <v>4.78498081485125</v>
+        <v>4.772773090720303</v>
       </c>
       <c r="N4" t="n">
-        <v>31.10837674700241</v>
+        <v>31.0058847563579</v>
       </c>
       <c r="O4" t="n">
-        <v>5.577488390575314</v>
+        <v>5.568292804474088</v>
       </c>
       <c r="P4" t="n">
-        <v>172.1808208856166</v>
+        <v>172.1790673210377</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26929,7 +27022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E823"/>
+  <dimension ref="A1:E826"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49153,6 +49246,87 @@
         </is>
       </c>
     </row>
+    <row r="824">
+      <c r="A824" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>-39.33605361801024,176.93766318153277</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>-39.336634198672634,176.93582776885432</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>-39.33604398015441,176.937661578559</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>-39.336617635219774,176.93580120625262</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>-39.33604139221163,176.93766114813093</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>-39.33815780276676,176.93707851525744</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>-39.33661160702266,176.93579153891426</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
